--- a/Employee_Test_cases.xlsx
+++ b/Employee_Test_cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Python for Data Science\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Python for Data Science\Projects\Data-quality-test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A31CC7-0491-47D0-A168-8D65672284CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CFA913-C073-4812-BF56-1D51C2368FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Employee_Test_cases.xlsx
+++ b/Employee_Test_cases.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Python for Data Science\Projects\Data-quality-test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CFA913-C073-4812-BF56-1D51C2368FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE0ADAC-284D-4985-AC70-C242D2018562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Plan" sheetId="2" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -57,14 +58,7 @@
     <t>TC_EMP_STRUCT_004</t>
   </si>
   <si>
-    <t>TC_EMP_STRUCT_005</t>
-  </si>
-  <si>
     <t>Verify that employee CSV File can be loaded successfully</t>
-  </si>
-  <si>
-    <t>Employee CSV file exists at the specified location
-File access permissions are available</t>
   </si>
   <si>
     <t>1: Locate the employee CSV File
@@ -82,20 +76,65 @@
     <t>Verify that The required columns are present in the CSV file</t>
   </si>
   <si>
-    <t>It is possible to load CSV file using CSV Reader
-CSV file exists and is accessible (state, not an action)</t>
+    <t>The CSV file contains the following columns: ID, Name, Surname, Department, Salary 
+No required column is missing</t>
+  </si>
+  <si>
+    <t>CSV file structure is validated and ready for further validation</t>
+  </si>
+  <si>
+    <t>Verify that the employee CSV file is not empty</t>
+  </si>
+  <si>
+    <t>Employee file can be loaded successfully</t>
+  </si>
+  <si>
+    <t>The file includes at least one row</t>
+  </si>
+  <si>
+    <t>CSV Data is available for the further validation</t>
+  </si>
+  <si>
+    <t>It is possible to load CSV file using CSV Reader;
+CSV file is not empty</t>
+  </si>
+  <si>
+    <t>Employee CSV file exists at the specified location;
+File access permissions are available</t>
+  </si>
+  <si>
+    <t>1: Load the Employee CSV File
+2: Check if at least one row exists in the file</t>
   </si>
   <si>
     <t>1: Load CSV file using CSV reader
 2: Read the column names from the CSV file
-3: Check if the given output will be the same as expected list of column names</t>
-  </si>
-  <si>
-    <t>The CSV file contains the following columns: ID, Name, Surname, Department, Salary 
-No required column is missing</t>
-  </si>
-  <si>
-    <t>CSV file structure is validated and ready for further validation</t>
+3: Check if the column names match the expected list of required columns</t>
+  </si>
+  <si>
+    <t>TC_EMP_INT_001</t>
+  </si>
+  <si>
+    <t>TC_EMP_INT_002</t>
+  </si>
+  <si>
+    <t>TC_EMP_INT_003</t>
+  </si>
+  <si>
+    <t>Verify that the CSF file exists on the specific location</t>
+  </si>
+  <si>
+    <t>1: Locate the Employee CSV file
+2: Verify that the file exists on the location</t>
+  </si>
+  <si>
+    <t>The Employee CSV file exists on the specific location</t>
+  </si>
+  <si>
+    <t>The Employee CSV file is stored at the specified location.</t>
+  </si>
+  <si>
+    <t>CSV file is available for further validation</t>
   </si>
 </sst>
 </file>
@@ -137,13 +176,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,8 +469,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A60B35-9A7A-479A-87E1-04083681AFEF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -452,131 +506,171 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Employee_Test_cases.xlsx
+++ b/Employee_Test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Python for Data Science\Projects\Data-quality-test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE0ADAC-284D-4985-AC70-C242D2018562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133669ED-1546-49CC-8CFF-66E142DA35C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -70,9 +70,6 @@
 No errors or exceptions occur during loading</t>
   </si>
   <si>
-    <t>CSV Data is available for further validation</t>
-  </si>
-  <si>
     <t>Verify that The required columns are present in the CSV file</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
 No required column is missing</t>
   </si>
   <si>
-    <t>CSV file structure is validated and ready for further validation</t>
-  </si>
-  <si>
     <t>Verify that the employee CSV file is not empty</t>
   </si>
   <si>
@@ -90,9 +84,6 @@
   </si>
   <si>
     <t>The file includes at least one row</t>
-  </si>
-  <si>
-    <t>CSV Data is available for the further validation</t>
   </si>
   <si>
     <t>It is possible to load CSV file using CSV Reader;
@@ -135,6 +126,93 @@
   </si>
   <si>
     <t>CSV file is available for further validation</t>
+  </si>
+  <si>
+    <t>CSV file is accesible and not empty</t>
+  </si>
+  <si>
+    <t>Verify that salary cells have positive numbers</t>
+  </si>
+  <si>
+    <t>TC_EMP_INT_004</t>
+  </si>
+  <si>
+    <t>TC_EMP_INT_005</t>
+  </si>
+  <si>
+    <t>Verify that ID is unique</t>
+  </si>
+  <si>
+    <t>CSV file is accesible, none of the cells are empty/Null</t>
+  </si>
+  <si>
+    <t>CSV file is accesible, ID cells are filled and integer</t>
+  </si>
+  <si>
+    <t>1: Load the CSV file using CSV reader
+2: All the cells include data and is not Null/empty
+3: ID is integer in every cells
+4: Observe that ID is unique for every row</t>
+  </si>
+  <si>
+    <t>1: Locate the employee CSV File
+2: Load the CSV file using CSV reader
+3: Observe that all the cells include data and is not Null/empty</t>
+  </si>
+  <si>
+    <t>1: Load the CSV file using CSV reader
+2: All the cells include data and is not Null/empty
+3: Observe ID is integer in every cells</t>
+  </si>
+  <si>
+    <t>1: Load the CSV file using CSV reader
+2: All the cells include data and is not Null/empty
+3: Observe that Salary rows are filled with Integer numbers</t>
+  </si>
+  <si>
+    <t>All salary cells are filled with Integer numbers</t>
+  </si>
+  <si>
+    <t>1: Load the CSV file using CSV reader
+2: All the cells include data and is not Null/empty
+3: Salary rows are filled with Integer numbers
+4: Observe that salary is always positive numbers</t>
+  </si>
+  <si>
+    <t>All the salary cells are filled with positive numbers</t>
+  </si>
+  <si>
+    <t>Verify that required fields contain no null/empty values</t>
+  </si>
+  <si>
+    <t>The following row cells in the CSV file are filled and there're no empty/Null cells: ID,Name, Surname, Department, Salary</t>
+  </si>
+  <si>
+    <t>All rows have unique ID values</t>
+  </si>
+  <si>
+    <t>Verify that all ID values are of integer type</t>
+  </si>
+  <si>
+    <t>All ID values are integers and can be safely used as identifiers</t>
+  </si>
+  <si>
+    <t>Verify that Salary contains numeric values (integer in this dataset)</t>
+  </si>
+  <si>
+    <t>CSV file is validated and ready for further checks</t>
+  </si>
+  <si>
+    <t>CSV file data is validated and ready for further checks</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
 </sst>
 </file>
@@ -176,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -190,11 +268,211 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -479,14 +757,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="6" width="40.42578125" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="48.28515625" customWidth="1"/>
+    <col min="5" max="5" width="40.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,28 +788,34 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -534,7 +823,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>11</v>
@@ -542,97 +831,163 @@
       <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F3" s="4"/>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+      <c r="G4" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="4"/>
+      <c r="G5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -640,7 +995,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -648,7 +1003,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -656,7 +1011,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -664,7 +1019,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -674,6 +1029,35 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"PASSED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+      <formula>"FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"Skipped"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"Deffered"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"Out of Scope"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G10" xr:uid="{D1BD1BE2-C365-4D2B-BCC0-BFAA3B31849F}">
+      <formula1>"Not Started,In Progress,Passed,Failed,Blocked,Deferred,Out of Scope"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>